--- a/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est dans la cuisine avec papa. Un petit pot de basilic est sur la table. Les feuilles sont un peu molles. Papa dit : elle a besoin d'eau. Elle a besoin de lumière. Aurore prend l'arrosoir avec papa. Un adulte est avec elle. Ils versent un peu d'eau. La terre devient sombre. Ça sent le basilic. Aurore touche une feuille. C'est doux. Papa pose le pot près de la fenêtre. La lumière arrive. Parce qu'il y a de l'eau et de la lumière, la plante tient mieux. Plus tard, Aurore revient. Les feuilles sont plus droites. Papa dit : on arrose avec un adulte. Aurore verse encore un tout petit peu. L'eau tombe tout doux. Papa range l'arrosoir. Aurore regarde la lumière sur les feuilles. Elle dit : eau, lumière, adulte. Papa sourit.</t>
+          <t>Aurore est dans la cuisine avec papa. Un petit pot de basilic est sur la table. Les feuilles sont un peu molles. Elle a besoin d'eau. Elle a besoin de lumière. Aurore prend l'arrosoir avec papa. Un adulte est avec elle. Ils versent un peu d'eau. La terre devient sombre. Ça sent le basilic. Aurore touche une feuille. C'est doux. Papa pose le pot près de la fenêtre. La lumière arrive. Parce qu'il y a de l'eau et de la lumière, la plante tient mieux. Plus tard, Aurore revient. Les feuilles sont plus droites. On arrose avec un adulte. Aurore verse encore un tout petit peu. L'eau tombe tout doux. Papa range l'arrosoir. Aurore regarde la lumière sur les feuilles. Eau, lumière, adulte. Papa sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore est dans la cuisine avec papa. Un petit pot de basilic est sur la table. Les feuilles sont un peu molles.
+papa|Elle a besoin d'eau. Elle a besoin de lumière.
+narrateur|Aurore prend l'arrosoir avec papa. Un adulte est avec elle. Ils versent un peu d'eau. La terre devient sombre. Ça sent le basilic. Aurore touche une feuille. C'est doux. Papa pose le pot près de la fenêtre. La lumière arrive. Parce qu'il y a de l'eau et de la lumière, la plante tient mieux. Plus tard, Aurore revient. Les feuilles sont plus droites.
+papa|On arrose avec un adulte.
+narrateur|Aurore verse encore un tout petit peu. L'eau tombe tout doux. Papa range l'arrosoir. Aurore regarde la lumière sur les feuilles.
+narrateur|Eau, lumière, adulte. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a soif. Que fait Aurore avec papa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore range l'arrosoir. La plante tient droit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Eau, lumière, adulte. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|La plante a soif. Que fait Aurore avec papa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,7 @@
           <t>narrateur|Aurore a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1844,7 @@
           <t>narrateur|Aurore range l'arrosoir. La plante tient droit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurore arrose le basilic</t>
+          <t>Le basilic trop au soleil</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut une feuille de basilic pour son pain. Le soleil est trop fort. Les feuilles cuisent. Ils arrosent, puis déplacent le pot à l'ombre du rideau.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est dans la cuisine avec papa. Un petit pot de basilic est sur la table. Les feuilles sont un peu molles. Elle a besoin d'eau. Elle a besoin de lumière. Aurore prend l'arrosoir avec papa. Un adulte est avec elle. Ils versent un peu d'eau. La terre devient sombre. Ça sent le basilic. Aurore touche une feuille. C'est doux. Papa pose le pot près de la fenêtre. La lumière arrive. Parce qu'il y a de l'eau et de la lumière, la plante tient mieux. Plus tard, Aurore revient. Les feuilles sont plus droites. On arrose avec un adulte. Aurore verse encore un tout petit peu. L'eau tombe tout doux. Papa range l'arrosoir. Aurore regarde la lumière sur les feuilles. Eau, lumière, adulte. Papa sourit.</t>
+          <t>Le carrelage brûle un peu les pieds. Un rai de soleil coupe la table en deux. Le pain de midi attend, encore tiède. Ça sent la croûte et le beurre. Nina vit ici, avec papa. Tu veux du basilic sur le pain ? Oui. Une feuille qui sent fort. En ce moment, Nina va vers la fenêtre. Le pot est dans le rai, tout blanc. Les feuilles sont molles, un peu jaunes. Elles sont chaudes. Trop de soleil. Il cuit, le pauvre. Nina touche la terre. La terre est chaude et sèche. Il a soif aussi. Oui. On lui donne de l'eau d'abord ? D'abord l'eau. Papa glisse l'arrosoir vers elle. L'anse est tiède, le plastique aussi. Nina tient avec lui. L'eau tombe, puis fume un tout petit peu. La terre fume ! Elle était trop chaude. On va le déplacer après. Où ? À côté, sous le rideau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurore est dans la cuisine avec papa. Un petit pot de basilic est sur la table. Les feuilles sont un peu molles. Papa dit : elle a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Aurore prend l'arrosoir avec papa. Un adulte est avec elle. Ils versent un peu d'eau. La terre devient sombre. Ça sent le basilic. Aurore touche une feuille. C'est doux. Papa pose le pot près de la fenêtre. La lumière arrive. Parce qu'il y a de l'eau et de la lumière, la plante tient mieux. Plus tard, Aurore revient. Les feuilles sont plus droites. Papa dit : on arrose avec un adulte. Aurore verse encore un tout petit peu. L'eau tombe tout doux. Papa range l'arrosoir. Aurore regarde la lumière sur les feuilles. Elle dit : eau, lumière, adulte. Papa sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le carrelage brûle un peu les pieds. Un rai de soleil coupe la table en deux. Le pain de midi attend, encore tiède. Ça sent la croûte et le beurre. Nina vit ici, avec papa. Tu veux du basilic sur le pain ? Oui. Une feuille qui sent fort. En ce moment, Nina va vers la fenêtre. Le pot est dans le rai, tout blanc. Les feuilles sont molles, un peu jaunes. Elles sont chaudes. Trop de soleil. Il cuit, le pauvre. Nina touche la terre. La terre est chaude et sèche. Il a soif aussi. Oui. On lui donne de l'eau d'abord ? D'abord l'eau. Papa glisse l'arrosoir vers elle. L'anse est tiède, le plastique aussi. Nina tient avec lui. L'eau tombe, puis fume un tout petit peu. La terre fume ! Elle était trop chaude. On va le déplacer après. Où ? À côté, sous le rideau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,35 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aurore est dans la cuisine avec papa. Un petit pot de basilic est sur la table. Les feuilles sont un peu molles.
-papa|Elle a besoin d'eau. Elle a besoin de lumière.
-narrateur|Aurore prend l'arrosoir avec papa. Un adulte est avec elle. Ils versent un peu d'eau. La terre devient sombre. Ça sent le basilic. Aurore touche une feuille. C'est doux. Papa pose le pot près de la fenêtre. La lumière arrive. Parce qu'il y a de l'eau et de la lumière, la plante tient mieux. Plus tard, Aurore revient. Les feuilles sont plus droites.
-papa|On arrose avec un adulte.
-narrateur|Aurore verse encore un tout petit peu. L'eau tombe tout doux. Papa range l'arrosoir. Aurore regarde la lumière sur les feuilles.
-narrateur|Eau, lumière, adulte. Papa sourit.</t>
+          <t>narrateur|Le carrelage brûle un peu les pieds.
+narrateur|Un rai de soleil coupe la table en deux.
+narrateur|Le pain de midi attend, encore tiède.
+narrateur|Ça sent la croûte et le beurre.
+narrateur|Nina vit ici, avec papa.
+papa|Tu veux du basilic sur le pain ?
+enfant-f|Oui.
+enfant-f|Une feuille qui sent fort.
+narrateur|En ce moment, Nina va vers la fenêtre.
+narrateur|Le pot est dans le rai, tout blanc.
+narrateur|Les feuilles sont molles, un peu jaunes.
+enfant-f|Elles sont chaudes.
+papa|Trop de soleil.
+papa|Il cuit, le pauvre.
+narrateur|Nina touche la terre.
+narrateur|La terre est chaude et sèche.
+enfant-f|Il a soif aussi.
+papa|Oui.
+papa|On lui donne de l'eau d'abord ?
+enfant-f|D'abord l'eau.
+narrateur|Papa glisse l'arrosoir vers elle.
+narrateur|L'anse est tiède, le plastique aussi.
+narrateur|Nina tient avec lui.
+narrateur|L'eau tombe, puis fume un tout petit peu.
+enfant-f|La terre fume !
+papa|Elle était trop chaude.
+papa|On va le déplacer après.
+enfant-f|Où ?
+papa|À côté, sous le rideau.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,12 +1384,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La plante a soif. Que fait Aurore avec papa ?</t>
+          <t>La plante a soif. Que fait Nina avec papa ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La plante a soif. Que fait Aurore avec papa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La plante a soif. Que fait Nina avec papa ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1384,7 +1419,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils versent de l'eau. Que fait Aurore ?</t>
+          <t>Ils versent de l'eau. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1433,7 +1468,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1540,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La plante a soif. Que fait Aurore avec papa ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La plante a soif.
+narrateur|Que fait Nina avec papa ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1568,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aurore a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
+          <t>Nina pose l'arrosoir. Le pot est encore dans le rai blanc. On le prend à deux ? Oui. Nina tient le bord du pot. La terre cuite est chaude sous les doigts. Papa tient le fond. Ils glissent le pot hors du rai. Le rideau fait une ombre mauve. Ici ? Ici. Il voit encore le jour. Mais plus le feu du soleil. Une feuille qui pendait se calme. Elle ne se redresse pas encore. Elle est fatiguée. Oui. Merci, Nina. Tu as bougé le pot. Le pain attend toujours sur la table. La croûte a refroidi, un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurore a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Papa, l'adulte, était avec elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina pose l'arrosoir. Le pot est encore dans le rai blanc. On le prend à deux ? Oui. Nina tient le bord du pot. La terre cuite est chaude sous les doigts. Papa tient le fond. Ils glissent le pot hors du rai. Le rideau fait une ombre mauve. Ici ? Ici. Il voit encore le jour. Mais plus le feu du soleil. Une feuille qui pendait se calme. Elle ne se redresse pas encore. Elle est fatiguée. Oui. Merci, Nina. Tu as bougé le pot. Le pain attend toujours sur la table. La croûte a refroidi, un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1601,7 +1636,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,10 +1712,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aurore a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina pose l'arrosoir.
+narrateur|Le pot est encore dans le rai blanc.
+papa|On le prend à deux ?
+enfant-f|Oui.
+narrateur|Nina tient le bord du pot.
+narrateur|La terre cuite est chaude sous les doigts.
+narrateur|Papa tient le fond.
+narrateur|Ils glissent le pot hors du rai.
+narrateur|Le rideau fait une ombre mauve.
+enfant-f|Ici ?
+papa|Ici.
+papa|Il voit encore le jour.
+papa|Mais plus le feu du soleil.
+narrateur|Une feuille qui pendait se calme.
+narrateur|Elle ne se redresse pas encore.
+enfant-f|Elle est fatiguée.
+papa|Oui.
+papa|Merci, Nina.
+papa|Tu as bougé le pot.
+narrateur|Le pain attend toujours sur la table.
+narrateur|La croûte a refroidi, un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,12 +1759,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aurore range l'arrosoir. La plante tient droit.</t>
+          <t>Nina choisit une feuille à l'ombre. Celle-là est encore bien verte. On en prend une petite. Le basilic se repose. Je la froisse ? Tout doux, oui. L'odeur arrive, moins brûlée. Elle sent le vert, enfin. Sur le pain. Nina pose la feuille sur le beurre. Le beurre fond un peu autour. Tu as aidé le basilic. Eau, puis ombre. Il cuit plus, là ? Non. Le rideau le garde. Le rai blanc reste sur la table, vide. Le pot respire dans le mauve. Tu as fini ta tartine ? Presque. Nina reprend une bouchée. Le beurre sent encore le vert.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurore range l'arrosoir. La plante tient droit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina choisit une feuille à l'ombre. Celle-là est encore bien verte. On en prend une petite. Le basilic se repose. Je la froisse ? Tout doux, oui. L'odeur arrive, moins brûlée. Elle sent le vert, enfin. Sur le pain. Nina pose la feuille sur le beurre. Le beurre fond un peu autour. Tu as aidé le basilic. Eau, puis ombre. Il cuit plus, là ? Non. Le rideau le garde. Le rai blanc reste sur la table, vide. Le pot respire dans le mauve. Tu as fini ta tartine ? Presque. Nina reprend une bouchée. Le beurre sent encore le vert.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1773,7 +1827,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1895,30 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aurore range l'arrosoir. La plante tient droit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina choisit une feuille à l'ombre.
+narrateur|Celle-là est encore bien verte.
+papa|On en prend une petite.
+papa|Le basilic se repose.
+enfant-f|Je la froisse ?
+papa|Tout doux, oui.
+narrateur|L'odeur arrive, moins brûlée.
+narrateur|Elle sent le vert, enfin.
+enfant-f|Sur le pain.
+narrateur|Nina pose la feuille sur le beurre.
+narrateur|Le beurre fond un peu autour.
+papa|Tu as aidé le basilic.
+papa|Eau, puis ombre.
+enfant-f|Il cuit plus, là ?
+papa|Non.
+papa|Le rideau le garde.
+narrateur|Le rai blanc reste sur la table, vide.
+narrateur|Le pot respire dans le mauve.
+papa|Tu as fini ta tartine ?
+enfant-f|Presque.
+narrateur|Nina reprend une bouchée.
+narrateur|Le beurre sent encore le vert.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina croque le pain. Le basilic est frais sur le beurre. Il sent bon. Oui. Parce qu'il n'a plus trop chaud. L'ombre du rideau est douce sur le pot.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina croque le pain. Le basilic est frais sur le beurre. Il sent bon. Oui. Parce qu'il n'a plus trop chaud. L'ombre du rideau est douce sur le pot.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1930,14 +2004,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2009,10 +2083,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina croque le pain.
+narrateur|Le basilic est frais sur le beurre.
+enfant-f|Il sent bon.
+papa|Oui.
+papa|Parce qu'il n'a plus trop chaud.
+narrateur|L'ombre du rideau est douce sur le pot.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurore, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
